--- a/forms_mapping.xlsx
+++ b/forms_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F5EC72-9C7D-4824-9906-34A5BED85636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BF751E-0EB4-4C31-9E36-EDB919F02077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="75">
   <si>
     <t>form_key</t>
   </si>
@@ -250,6 +250,18 @@
   </si>
   <si>
     <t>consumo_xius</t>
+  </si>
+  <si>
+    <t>nuevo</t>
+  </si>
+  <si>
+    <t>entry.821239971</t>
+  </si>
+  <si>
+    <t>entry.1822810394</t>
+  </si>
+  <si>
+    <t>cambio</t>
   </si>
 </sst>
 </file>
@@ -649,7 +661,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF6FF24-64F9-4D1C-AEDC-54B01573F003}">
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -908,193 +920,215 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>68</v>
       </c>
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
         <v>19</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
         <v>19</v>
       </c>
       <c r="D23" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
         <v>19</v>
       </c>
       <c r="D24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C29" t="s">
         <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C30" t="s">
         <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
         <v>64</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
         <v>64</v>
       </c>
       <c r="D32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>34</v>
-      </c>
-      <c r="D41" t="s">
-        <v>25</v>
-      </c>
-      <c r="E41" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" t="s">
-        <v>31</v>
+        <v>34</v>
+      </c>
+      <c r="D43" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>30</v>
       </c>
     </row>
